--- a/BASE DATOS ACTUALIZADA.xlsx
+++ b/BASE DATOS ACTUALIZADA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reyesc\Documents\New project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FB533D-1F11-4BA4-84F3-91FF55855F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BFFA15-5EE5-47AA-AFA6-6CCD4B4FCF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40985152-455C-4ECA-8C08-C5A378BF46CE}"/>
   </bookViews>
@@ -8506,7 +8506,9 @@
       <c r="M111" s="9">
         <v>4561600.7837957228</v>
       </c>
-      <c r="N111" s="9"/>
+      <c r="N111" s="9">
+        <v>0</v>
+      </c>
       <c r="O111" s="9">
         <f t="shared" si="15"/>
         <v>4561600.7837957228</v>
@@ -8572,7 +8574,9 @@
       <c r="M112" s="9">
         <v>4561600.7837957228</v>
       </c>
-      <c r="N112" s="9"/>
+      <c r="N112" s="9">
+        <v>0</v>
+      </c>
       <c r="O112" s="9">
         <f t="shared" si="15"/>
         <v>4561600.7837957228</v>
@@ -8612,9 +8616,13 @@
         <f>SUBTOTAL(109,Tabla1[Monto Presupuesto RD$])</f>
         <v>267612954.1207777</v>
       </c>
+      <c r="N113" s="29">
+        <f>SUBTOTAL(109,Tabla1[[Monto Adjudicado ]])</f>
+        <v>178926844.62000012</v>
+      </c>
       <c r="O113" s="9">
         <f t="shared" ref="O113:O125" si="24">M113-N113</f>
-        <v>267612954.1207777</v>
+        <v>88686109.500777572</v>
       </c>
     </row>
     <row r="114" spans="13:15" x14ac:dyDescent="0.3">
